--- a/artfynd/A 221-2025 artfynd.xlsx
+++ b/artfynd/A 221-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122330549</v>
+        <v>122330431</v>
       </c>
       <c r="B2" t="n">
-        <v>100441</v>
+        <v>94793</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>651558</v>
+        <v>651557</v>
       </c>
       <c r="R2" t="n">
-        <v>6673856</v>
+        <v>6673863</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,7 +791,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122330431</v>
+        <v>122330411</v>
       </c>
       <c r="B3" t="n">
         <v>94793</v>
@@ -826,7 +826,11 @@
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -835,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>651557</v>
+        <v>651579</v>
       </c>
       <c r="R3" t="n">
-        <v>6673863</v>
+        <v>6673877</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -870,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +884,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,10 +911,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122330411</v>
+        <v>122330549</v>
       </c>
       <c r="B4" t="n">
-        <v>94793</v>
+        <v>100441</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,30 +927,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>210</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -955,10 +955,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>651579</v>
+        <v>651558</v>
       </c>
       <c r="R4" t="n">
-        <v>6673877</v>
+        <v>6673856</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -990,7 +990,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,10 +1027,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122330389</v>
+        <v>122330382</v>
       </c>
       <c r="B5" t="n">
-        <v>90549</v>
+        <v>79686</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1043,21 +1043,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3215</v>
+        <v>229497</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1070,10 +1070,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>651607</v>
+        <v>651650</v>
       </c>
       <c r="R5" t="n">
-        <v>6673967</v>
+        <v>6673900</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1124,8 +1124,24 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1139,6 +1155,121 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>122330389</v>
+      </c>
+      <c r="B6" t="n">
+        <v>90549</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ackareåsen, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>651607</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6673967</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 221-2025 artfynd.xlsx
+++ b/artfynd/A 221-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122330431</v>
+        <v>122330411</v>
       </c>
       <c r="B2" t="n">
-        <v>94793</v>
+        <v>94803</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,11 @@
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -719,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>651557</v>
+        <v>651579</v>
       </c>
       <c r="R2" t="n">
-        <v>6673863</v>
+        <v>6673877</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -754,7 +758,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +768,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122330411</v>
+        <v>122330431</v>
       </c>
       <c r="B3" t="n">
-        <v>94793</v>
+        <v>94803</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -826,11 +830,7 @@
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>651579</v>
+        <v>651557</v>
       </c>
       <c r="R3" t="n">
-        <v>6673877</v>
+        <v>6673863</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,7 +914,7 @@
         <v>122330549</v>
       </c>
       <c r="B4" t="n">
-        <v>100441</v>
+        <v>100451</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>122330382</v>
       </c>
       <c r="B5" t="n">
-        <v>79686</v>
+        <v>79687</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>122330389</v>
       </c>
       <c r="B6" t="n">
-        <v>90549</v>
+        <v>90559</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 221-2025 artfynd.xlsx
+++ b/artfynd/A 221-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122330411</v>
+        <v>122330549</v>
       </c>
       <c r="B2" t="n">
-        <v>94803</v>
+        <v>100463</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,30 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>210</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -723,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>651579</v>
+        <v>651558</v>
       </c>
       <c r="R2" t="n">
-        <v>6673877</v>
+        <v>6673856</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -758,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -768,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -798,7 +794,7 @@
         <v>122330431</v>
       </c>
       <c r="B3" t="n">
-        <v>94803</v>
+        <v>94815</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -911,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122330549</v>
+        <v>122330411</v>
       </c>
       <c r="B4" t="n">
-        <v>100451</v>
+        <v>94815</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,26 +923,30 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>210</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -955,10 +955,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>651558</v>
+        <v>651579</v>
       </c>
       <c r="R4" t="n">
-        <v>6673856</v>
+        <v>6673877</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -990,7 +990,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,7 +1030,7 @@
         <v>122330382</v>
       </c>
       <c r="B5" t="n">
-        <v>79687</v>
+        <v>79692</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>122330389</v>
       </c>
       <c r="B6" t="n">
-        <v>90559</v>
+        <v>90571</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 221-2025 artfynd.xlsx
+++ b/artfynd/A 221-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122330549</v>
+        <v>122330411</v>
       </c>
       <c r="B2" t="n">
-        <v>100463</v>
+        <v>94820</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,30 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -719,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>651558</v>
+        <v>651579</v>
       </c>
       <c r="R2" t="n">
-        <v>6673856</v>
+        <v>6673877</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -754,7 +758,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +768,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122330431</v>
+        <v>122330549</v>
       </c>
       <c r="B3" t="n">
-        <v>94815</v>
+        <v>100468</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,21 +811,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>210</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -835,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>651557</v>
+        <v>651558</v>
       </c>
       <c r="R3" t="n">
-        <v>6673863</v>
+        <v>6673856</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -870,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +884,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,10 +911,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122330411</v>
+        <v>122330431</v>
       </c>
       <c r="B4" t="n">
-        <v>94815</v>
+        <v>94820</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -942,11 +946,7 @@
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -955,10 +955,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>651579</v>
+        <v>651557</v>
       </c>
       <c r="R4" t="n">
-        <v>6673877</v>
+        <v>6673863</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -990,7 +990,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1161,7 +1161,7 @@
         <v>122330389</v>
       </c>
       <c r="B6" t="n">
-        <v>90571</v>
+        <v>90575</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 221-2025 artfynd.xlsx
+++ b/artfynd/A 221-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122330411</v>
       </c>
       <c r="B2" t="n">
-        <v>94820</v>
+        <v>94829</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,11 +692,6 @@
       </c>
       <c r="E2" t="n">
         <v>210</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Grön sköldmossa</t>
-        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -795,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122330549</v>
+        <v>122330431</v>
       </c>
       <c r="B3" t="n">
-        <v>100468</v>
+        <v>94829</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,21 +806,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
+        <v>210</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -839,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>651558</v>
+        <v>651557</v>
       </c>
       <c r="R3" t="n">
-        <v>6673856</v>
+        <v>6673863</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -874,7 +864,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -884,7 +874,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122330431</v>
+        <v>122330549</v>
       </c>
       <c r="B4" t="n">
-        <v>94820</v>
+        <v>100477</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,21 +917,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>210</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Grön sköldmossa</t>
-        </is>
+        <v>222498</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -955,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>651557</v>
+        <v>651558</v>
       </c>
       <c r="R4" t="n">
-        <v>6673863</v>
+        <v>6673856</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -990,7 +975,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1000,7 +985,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,7 +1015,7 @@
         <v>122330382</v>
       </c>
       <c r="B5" t="n">
-        <v>79692</v>
+        <v>79693</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1044,11 +1029,6 @@
       </c>
       <c r="E5" t="n">
         <v>229497</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Korallblylav</t>
-        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1128,11 +1108,6 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
       <c r="AK5" t="inlineStr">
         <is>
           <t>Populus tremula</t>
@@ -1161,7 +1136,7 @@
         <v>122330389</v>
       </c>
       <c r="B6" t="n">
-        <v>90575</v>
+        <v>90580</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1175,11 +1150,6 @@
       </c>
       <c r="E6" t="n">
         <v>3215</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Rödgul trumpetsvamp</t>
-        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>

--- a/artfynd/A 221-2025 artfynd.xlsx
+++ b/artfynd/A 221-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122330411</v>
+        <v>122330431</v>
       </c>
       <c r="B2" t="n">
-        <v>94829</v>
+        <v>94842</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -693,6 +693,11 @@
       <c r="E2" t="n">
         <v>210</v>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>Buxbaumia viridis</t>
@@ -705,11 +710,7 @@
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -718,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>651579</v>
+        <v>651557</v>
       </c>
       <c r="R2" t="n">
-        <v>6673877</v>
+        <v>6673863</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -753,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122330431</v>
+        <v>122330411</v>
       </c>
       <c r="B3" t="n">
-        <v>94829</v>
+        <v>94842</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,6 +809,11 @@
       <c r="E3" t="n">
         <v>210</v>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>Buxbaumia viridis</t>
@@ -820,7 +826,11 @@
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -829,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>651557</v>
+        <v>651579</v>
       </c>
       <c r="R3" t="n">
-        <v>6673863</v>
+        <v>6673877</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -864,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -874,7 +884,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,7 +914,7 @@
         <v>122330549</v>
       </c>
       <c r="B4" t="n">
-        <v>100477</v>
+        <v>100490</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -918,6 +928,11 @@
       </c>
       <c r="E4" t="n">
         <v>222498</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -1015,7 +1030,7 @@
         <v>122330382</v>
       </c>
       <c r="B5" t="n">
-        <v>79693</v>
+        <v>79697</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,6 +1044,11 @@
       </c>
       <c r="E5" t="n">
         <v>229497</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1108,6 +1128,11 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
       <c r="AK5" t="inlineStr">
         <is>
           <t>Populus tremula</t>
@@ -1136,7 +1161,7 @@
         <v>122330389</v>
       </c>
       <c r="B6" t="n">
-        <v>90580</v>
+        <v>90593</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1150,6 +1175,11 @@
       </c>
       <c r="E6" t="n">
         <v>3215</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>

--- a/artfynd/A 221-2025 artfynd.xlsx
+++ b/artfynd/A 221-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122330431</v>
       </c>
       <c r="B2" t="n">
-        <v>94842</v>
+        <v>94855</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122330411</v>
+        <v>122330549</v>
       </c>
       <c r="B3" t="n">
-        <v>94842</v>
+        <v>100503</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,30 +807,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>210</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -839,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>651579</v>
+        <v>651558</v>
       </c>
       <c r="R3" t="n">
-        <v>6673877</v>
+        <v>6673856</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -874,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -884,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122330549</v>
+        <v>122330411</v>
       </c>
       <c r="B4" t="n">
-        <v>100490</v>
+        <v>94855</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,26 +923,30 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>210</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -955,10 +955,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>651558</v>
+        <v>651579</v>
       </c>
       <c r="R4" t="n">
-        <v>6673856</v>
+        <v>6673877</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -990,7 +990,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1161,7 +1161,7 @@
         <v>122330389</v>
       </c>
       <c r="B6" t="n">
-        <v>90593</v>
+        <v>90606</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 221-2025 artfynd.xlsx
+++ b/artfynd/A 221-2025 artfynd.xlsx
@@ -1161,7 +1161,7 @@
         <v>122330389</v>
       </c>
       <c r="B6" t="n">
-        <v>90606</v>
+        <v>90605</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 221-2025 artfynd.xlsx
+++ b/artfynd/A 221-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122330431</v>
+        <v>122330411</v>
       </c>
       <c r="B2" t="n">
-        <v>94855</v>
+        <v>94857</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,11 @@
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -719,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>651557</v>
+        <v>651579</v>
       </c>
       <c r="R2" t="n">
-        <v>6673863</v>
+        <v>6673877</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -754,7 +758,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +768,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122330549</v>
+        <v>122330431</v>
       </c>
       <c r="B3" t="n">
-        <v>100503</v>
+        <v>94857</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,21 +811,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>210</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -835,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>651558</v>
+        <v>651557</v>
       </c>
       <c r="R3" t="n">
-        <v>6673856</v>
+        <v>6673863</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -870,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +884,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,10 +911,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122330411</v>
+        <v>122330549</v>
       </c>
       <c r="B4" t="n">
-        <v>94855</v>
+        <v>100506</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,30 +927,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>210</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -955,10 +955,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>651579</v>
+        <v>651558</v>
       </c>
       <c r="R4" t="n">
-        <v>6673877</v>
+        <v>6673856</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -990,7 +990,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 221-2025 artfynd.xlsx
+++ b/artfynd/A 221-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122330411</v>
+        <v>122330549</v>
       </c>
       <c r="B2" t="n">
-        <v>94857</v>
+        <v>100506</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,30 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>210</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -723,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>651579</v>
+        <v>651558</v>
       </c>
       <c r="R2" t="n">
-        <v>6673877</v>
+        <v>6673856</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -758,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -768,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,7 +791,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122330431</v>
+        <v>122330411</v>
       </c>
       <c r="B3" t="n">
         <v>94857</v>
@@ -830,7 +826,11 @@
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>651557</v>
+        <v>651579</v>
       </c>
       <c r="R3" t="n">
-        <v>6673863</v>
+        <v>6673877</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,10 +911,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122330549</v>
+        <v>122330431</v>
       </c>
       <c r="B4" t="n">
-        <v>100506</v>
+        <v>94857</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,21 +927,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>210</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -955,10 +955,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>651558</v>
+        <v>651557</v>
       </c>
       <c r="R4" t="n">
-        <v>6673856</v>
+        <v>6673863</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -990,7 +990,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 221-2025 artfynd.xlsx
+++ b/artfynd/A 221-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122330549</v>
+        <v>122330431</v>
       </c>
       <c r="B2" t="n">
-        <v>100506</v>
+        <v>94858</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>651558</v>
+        <v>651557</v>
       </c>
       <c r="R2" t="n">
-        <v>6673856</v>
+        <v>6673863</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,7 +794,7 @@
         <v>122330411</v>
       </c>
       <c r="B3" t="n">
-        <v>94857</v>
+        <v>94858</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -911,10 +911,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122330431</v>
+        <v>122330549</v>
       </c>
       <c r="B4" t="n">
-        <v>94857</v>
+        <v>100507</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,21 +927,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>210</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -955,10 +955,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>651557</v>
+        <v>651558</v>
       </c>
       <c r="R4" t="n">
-        <v>6673863</v>
+        <v>6673856</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -990,7 +990,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,7 +1030,7 @@
         <v>122330382</v>
       </c>
       <c r="B5" t="n">
-        <v>79697</v>
+        <v>79698</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>122330389</v>
       </c>
       <c r="B6" t="n">
-        <v>90605</v>
+        <v>90606</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 221-2025 artfynd.xlsx
+++ b/artfynd/A 221-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122330431</v>
+        <v>122330411</v>
       </c>
       <c r="B2" t="n">
-        <v>94858</v>
+        <v>94861</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,11 @@
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -719,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>651557</v>
+        <v>651579</v>
       </c>
       <c r="R2" t="n">
-        <v>6673863</v>
+        <v>6673877</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -754,7 +758,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +768,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122330411</v>
+        <v>122330549</v>
       </c>
       <c r="B3" t="n">
-        <v>94858</v>
+        <v>100510</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,30 +811,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>210</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>651579</v>
+        <v>651558</v>
       </c>
       <c r="R3" t="n">
-        <v>6673877</v>
+        <v>6673856</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,10 +911,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122330549</v>
+        <v>122330431</v>
       </c>
       <c r="B4" t="n">
-        <v>100507</v>
+        <v>94861</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,21 +927,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>210</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -955,10 +955,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>651558</v>
+        <v>651557</v>
       </c>
       <c r="R4" t="n">
-        <v>6673856</v>
+        <v>6673863</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -990,7 +990,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,7 +1030,7 @@
         <v>122330382</v>
       </c>
       <c r="B5" t="n">
-        <v>79698</v>
+        <v>79701</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>122330389</v>
       </c>
       <c r="B6" t="n">
-        <v>90606</v>
+        <v>90609</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 221-2025 artfynd.xlsx
+++ b/artfynd/A 221-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1158,15 +1158,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122330389</v>
+        <v>129173786</v>
       </c>
       <c r="B6" t="n">
-        <v>90609</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92852</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1174,25 +1169,33 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3215</v>
+        <v>5964</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
@@ -1201,10 +1204,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>651607</v>
+        <v>651568</v>
       </c>
       <c r="R6" t="n">
-        <v>6673967</v>
+        <v>6673841</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1231,22 +1234,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Räknade en och en.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1270,6 +1278,1829 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129173764</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91296</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ackareåsen, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>651571</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6673850</v>
+      </c>
+      <c r="S7" t="n">
+        <v>4</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129173748</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57883</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ackareåsen, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>651578</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6673850</v>
+      </c>
+      <c r="S8" t="n">
+        <v>40</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129173765</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91296</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ackareåsen, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>651554</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6673844</v>
+      </c>
+      <c r="S9" t="n">
+        <v>4</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129173789</v>
+      </c>
+      <c r="B10" t="n">
+        <v>92852</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ackareåsen, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>651578</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6673861</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129173797</v>
+      </c>
+      <c r="B11" t="n">
+        <v>92852</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ackareåsen, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>651609</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6673882</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129173783</v>
+      </c>
+      <c r="B12" t="n">
+        <v>92818</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>788</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Gul taggsvamp</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hydnellum geogenium</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ackareåsen, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>651581</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6673839</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Jättestort mycel!</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129173766</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91296</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Ackareåsen, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>651587</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6673835</v>
+      </c>
+      <c r="S13" t="n">
+        <v>4</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129173767</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91296</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Ackareåsen, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>651595</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6673879</v>
+      </c>
+      <c r="S14" t="n">
+        <v>4</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129173794</v>
+      </c>
+      <c r="B15" t="n">
+        <v>92852</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Ackareåsen, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>651576</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6673868</v>
+      </c>
+      <c r="S15" t="n">
+        <v>4</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>122330389</v>
+      </c>
+      <c r="B16" t="n">
+        <v>90609</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Ackareåsen, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>651607</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6673967</v>
+      </c>
+      <c r="S16" t="n">
+        <v>4</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129173800</v>
+      </c>
+      <c r="B17" t="n">
+        <v>92852</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Ackareåsen, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>651637</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6673909</v>
+      </c>
+      <c r="S17" t="n">
+        <v>4</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129173801</v>
+      </c>
+      <c r="B18" t="n">
+        <v>92852</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Ackareåsen, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>651639</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6673915</v>
+      </c>
+      <c r="S18" t="n">
+        <v>4</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129173771</v>
+      </c>
+      <c r="B19" t="n">
+        <v>91296</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Ackareåsen, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>651627</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6673941</v>
+      </c>
+      <c r="S19" t="n">
+        <v>4</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>129173803</v>
+      </c>
+      <c r="B20" t="n">
+        <v>92852</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Ackareåsen, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>651592</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6673969</v>
+      </c>
+      <c r="S20" t="n">
+        <v>4</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>129173768</v>
+      </c>
+      <c r="B21" t="n">
+        <v>91296</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Ackareåsen, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>651594</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6673918</v>
+      </c>
+      <c r="S21" t="n">
+        <v>4</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>129173770</v>
+      </c>
+      <c r="B22" t="n">
+        <v>91296</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Ackareåsen, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>651640</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6673916</v>
+      </c>
+      <c r="S22" t="n">
+        <v>4</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 221-2025 artfynd.xlsx
+++ b/artfynd/A 221-2025 artfynd.xlsx
@@ -1161,7 +1161,7 @@
         <v>129173786</v>
       </c>
       <c r="B6" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>129173764</v>
       </c>
       <c r="B7" t="n">
-        <v>91296</v>
+        <v>91299</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         <v>129173765</v>
       </c>
       <c r="B9" t="n">
-        <v>91296</v>
+        <v>91299</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         <v>129173789</v>
       </c>
       <c r="B10" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>129173797</v>
       </c>
       <c r="B11" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>129173783</v>
       </c>
       <c r="B12" t="n">
-        <v>92818</v>
+        <v>92821</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
         <v>129173766</v>
       </c>
       <c r="B13" t="n">
-        <v>91296</v>
+        <v>91299</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>129173767</v>
       </c>
       <c r="B14" t="n">
-        <v>91296</v>
+        <v>91299</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>129173794</v>
       </c>
       <c r="B15" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>129173800</v>
       </c>
       <c r="B17" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>129173801</v>
       </c>
       <c r="B18" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2659,7 +2659,7 @@
         <v>129173771</v>
       </c>
       <c r="B19" t="n">
-        <v>91296</v>
+        <v>91299</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>129173803</v>
       </c>
       <c r="B20" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>129173768</v>
       </c>
       <c r="B21" t="n">
-        <v>91296</v>
+        <v>91299</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
         <v>129173770</v>
       </c>
       <c r="B22" t="n">
-        <v>91296</v>
+        <v>91299</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 221-2025 artfynd.xlsx
+++ b/artfynd/A 221-2025 artfynd.xlsx
@@ -1161,7 +1161,7 @@
         <v>129173786</v>
       </c>
       <c r="B6" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>129173764</v>
       </c>
       <c r="B7" t="n">
-        <v>91299</v>
+        <v>91305</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>129173748</v>
       </c>
       <c r="B8" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         <v>129173765</v>
       </c>
       <c r="B9" t="n">
-        <v>91299</v>
+        <v>91305</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         <v>129173789</v>
       </c>
       <c r="B10" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>129173797</v>
       </c>
       <c r="B11" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>129173783</v>
       </c>
       <c r="B12" t="n">
-        <v>92821</v>
+        <v>92828</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
         <v>129173766</v>
       </c>
       <c r="B13" t="n">
-        <v>91299</v>
+        <v>91305</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>129173767</v>
       </c>
       <c r="B14" t="n">
-        <v>91299</v>
+        <v>91305</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>129173794</v>
       </c>
       <c r="B15" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>129173800</v>
       </c>
       <c r="B17" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>129173801</v>
       </c>
       <c r="B18" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2659,7 +2659,7 @@
         <v>129173771</v>
       </c>
       <c r="B19" t="n">
-        <v>91299</v>
+        <v>91305</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>129173803</v>
       </c>
       <c r="B20" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>129173768</v>
       </c>
       <c r="B21" t="n">
-        <v>91299</v>
+        <v>91305</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
         <v>129173770</v>
       </c>
       <c r="B22" t="n">
-        <v>91299</v>
+        <v>91305</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 221-2025 artfynd.xlsx
+++ b/artfynd/A 221-2025 artfynd.xlsx
@@ -1161,7 +1161,7 @@
         <v>129173786</v>
       </c>
       <c r="B6" t="n">
-        <v>92862</v>
+        <v>92869</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>129173764</v>
       </c>
       <c r="B7" t="n">
-        <v>91305</v>
+        <v>91312</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         <v>129173765</v>
       </c>
       <c r="B9" t="n">
-        <v>91305</v>
+        <v>91312</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         <v>129173789</v>
       </c>
       <c r="B10" t="n">
-        <v>92862</v>
+        <v>92869</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>129173797</v>
       </c>
       <c r="B11" t="n">
-        <v>92862</v>
+        <v>92869</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>129173783</v>
       </c>
       <c r="B12" t="n">
-        <v>92828</v>
+        <v>92835</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
         <v>129173766</v>
       </c>
       <c r="B13" t="n">
-        <v>91305</v>
+        <v>91312</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>129173767</v>
       </c>
       <c r="B14" t="n">
-        <v>91305</v>
+        <v>91312</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>129173794</v>
       </c>
       <c r="B15" t="n">
-        <v>92862</v>
+        <v>92869</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>129173800</v>
       </c>
       <c r="B17" t="n">
-        <v>92862</v>
+        <v>92869</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>129173801</v>
       </c>
       <c r="B18" t="n">
-        <v>92862</v>
+        <v>92869</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2659,7 +2659,7 @@
         <v>129173771</v>
       </c>
       <c r="B19" t="n">
-        <v>91305</v>
+        <v>91312</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>129173803</v>
       </c>
       <c r="B20" t="n">
-        <v>92862</v>
+        <v>92869</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>129173768</v>
       </c>
       <c r="B21" t="n">
-        <v>91305</v>
+        <v>91312</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
         <v>129173770</v>
       </c>
       <c r="B22" t="n">
-        <v>91305</v>
+        <v>91312</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 221-2025 artfynd.xlsx
+++ b/artfynd/A 221-2025 artfynd.xlsx
@@ -1161,7 +1161,7 @@
         <v>129173786</v>
       </c>
       <c r="B6" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>129173764</v>
       </c>
       <c r="B7" t="n">
-        <v>91312</v>
+        <v>91314</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>129173748</v>
       </c>
       <c r="B8" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         <v>129173765</v>
       </c>
       <c r="B9" t="n">
-        <v>91312</v>
+        <v>91314</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         <v>129173789</v>
       </c>
       <c r="B10" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>129173797</v>
       </c>
       <c r="B11" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>129173783</v>
       </c>
       <c r="B12" t="n">
-        <v>92835</v>
+        <v>92837</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
         <v>129173766</v>
       </c>
       <c r="B13" t="n">
-        <v>91312</v>
+        <v>91314</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>129173767</v>
       </c>
       <c r="B14" t="n">
-        <v>91312</v>
+        <v>91314</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>129173794</v>
       </c>
       <c r="B15" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>129173800</v>
       </c>
       <c r="B17" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>129173801</v>
       </c>
       <c r="B18" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2659,7 +2659,7 @@
         <v>129173771</v>
       </c>
       <c r="B19" t="n">
-        <v>91312</v>
+        <v>91314</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>129173803</v>
       </c>
       <c r="B20" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>129173768</v>
       </c>
       <c r="B21" t="n">
-        <v>91312</v>
+        <v>91314</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
         <v>129173770</v>
       </c>
       <c r="B22" t="n">
-        <v>91312</v>
+        <v>91314</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 221-2025 artfynd.xlsx
+++ b/artfynd/A 221-2025 artfynd.xlsx
@@ -1161,7 +1161,7 @@
         <v>129173786</v>
       </c>
       <c r="B6" t="n">
-        <v>92871</v>
+        <v>92857</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>129173764</v>
       </c>
       <c r="B7" t="n">
-        <v>91314</v>
+        <v>91313</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         <v>129173765</v>
       </c>
       <c r="B9" t="n">
-        <v>91314</v>
+        <v>91313</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         <v>129173789</v>
       </c>
       <c r="B10" t="n">
-        <v>92871</v>
+        <v>92857</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>129173797</v>
       </c>
       <c r="B11" t="n">
-        <v>92871</v>
+        <v>92857</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>129173783</v>
       </c>
       <c r="B12" t="n">
-        <v>92837</v>
+        <v>92823</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
         <v>129173766</v>
       </c>
       <c r="B13" t="n">
-        <v>91314</v>
+        <v>91313</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>129173767</v>
       </c>
       <c r="B14" t="n">
-        <v>91314</v>
+        <v>91313</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>129173794</v>
       </c>
       <c r="B15" t="n">
-        <v>92871</v>
+        <v>92857</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>129173800</v>
       </c>
       <c r="B17" t="n">
-        <v>92871</v>
+        <v>92857</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>129173801</v>
       </c>
       <c r="B18" t="n">
-        <v>92871</v>
+        <v>92857</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2659,7 +2659,7 @@
         <v>129173771</v>
       </c>
       <c r="B19" t="n">
-        <v>91314</v>
+        <v>91313</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>129173803</v>
       </c>
       <c r="B20" t="n">
-        <v>92871</v>
+        <v>92857</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>129173768</v>
       </c>
       <c r="B21" t="n">
-        <v>91314</v>
+        <v>91313</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
         <v>129173770</v>
       </c>
       <c r="B22" t="n">
-        <v>91314</v>
+        <v>91313</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 221-2025 artfynd.xlsx
+++ b/artfynd/A 221-2025 artfynd.xlsx
@@ -1161,7 +1161,7 @@
         <v>129173786</v>
       </c>
       <c r="B6" t="n">
-        <v>92857</v>
+        <v>92858</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         <v>129173789</v>
       </c>
       <c r="B10" t="n">
-        <v>92857</v>
+        <v>92858</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>129173797</v>
       </c>
       <c r="B11" t="n">
-        <v>92857</v>
+        <v>92858</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>129173783</v>
       </c>
       <c r="B12" t="n">
-        <v>92823</v>
+        <v>92824</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>129173794</v>
       </c>
       <c r="B15" t="n">
-        <v>92857</v>
+        <v>92858</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2424,10 +2424,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129173800</v>
+        <v>129173801</v>
       </c>
       <c r="B17" t="n">
-        <v>92857</v>
+        <v>92858</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2454,14 +2454,10 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
@@ -2470,10 +2466,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>651637</v>
+        <v>651639</v>
       </c>
       <c r="R17" t="n">
-        <v>6673909</v>
+        <v>6673915</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2505,7 +2501,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2515,7 +2511,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2542,10 +2538,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129173801</v>
+        <v>129173800</v>
       </c>
       <c r="B18" t="n">
-        <v>92857</v>
+        <v>92858</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2572,10 +2568,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
@@ -2584,10 +2584,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>651639</v>
+        <v>651637</v>
       </c>
       <c r="R18" t="n">
-        <v>6673915</v>
+        <v>6673909</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2619,7 +2619,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2629,7 +2629,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2769,7 +2769,7 @@
         <v>129173803</v>
       </c>
       <c r="B20" t="n">
-        <v>92857</v>
+        <v>92858</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 221-2025 artfynd.xlsx
+++ b/artfynd/A 221-2025 artfynd.xlsx
@@ -1161,7 +1161,7 @@
         <v>129173786</v>
       </c>
       <c r="B6" t="n">
-        <v>92858</v>
+        <v>92861</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>129173764</v>
       </c>
       <c r="B7" t="n">
-        <v>91313</v>
+        <v>91316</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         <v>129173765</v>
       </c>
       <c r="B9" t="n">
-        <v>91313</v>
+        <v>91316</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         <v>129173789</v>
       </c>
       <c r="B10" t="n">
-        <v>92858</v>
+        <v>92861</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>129173797</v>
       </c>
       <c r="B11" t="n">
-        <v>92858</v>
+        <v>92861</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>129173783</v>
       </c>
       <c r="B12" t="n">
-        <v>92824</v>
+        <v>92827</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
         <v>129173766</v>
       </c>
       <c r="B13" t="n">
-        <v>91313</v>
+        <v>91316</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>129173767</v>
       </c>
       <c r="B14" t="n">
-        <v>91313</v>
+        <v>91316</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>129173794</v>
       </c>
       <c r="B15" t="n">
-        <v>92858</v>
+        <v>92861</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2424,10 +2424,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129173801</v>
+        <v>129173800</v>
       </c>
       <c r="B17" t="n">
-        <v>92858</v>
+        <v>92861</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2454,10 +2454,14 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
@@ -2466,10 +2470,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>651639</v>
+        <v>651637</v>
       </c>
       <c r="R17" t="n">
-        <v>6673915</v>
+        <v>6673909</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2501,7 +2505,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2511,7 +2515,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2538,10 +2542,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129173800</v>
+        <v>129173801</v>
       </c>
       <c r="B18" t="n">
-        <v>92858</v>
+        <v>92861</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2568,14 +2572,10 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
@@ -2584,10 +2584,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>651637</v>
+        <v>651639</v>
       </c>
       <c r="R18" t="n">
-        <v>6673909</v>
+        <v>6673915</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2619,7 +2619,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2629,7 +2629,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2659,7 +2659,7 @@
         <v>129173771</v>
       </c>
       <c r="B19" t="n">
-        <v>91313</v>
+        <v>91316</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>129173803</v>
       </c>
       <c r="B20" t="n">
-        <v>92858</v>
+        <v>92861</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>129173768</v>
       </c>
       <c r="B21" t="n">
-        <v>91313</v>
+        <v>91316</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
         <v>129173770</v>
       </c>
       <c r="B22" t="n">
-        <v>91313</v>
+        <v>91316</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 221-2025 artfynd.xlsx
+++ b/artfynd/A 221-2025 artfynd.xlsx
@@ -1161,7 +1161,7 @@
         <v>129173786</v>
       </c>
       <c r="B6" t="n">
-        <v>92861</v>
+        <v>92863</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>129173764</v>
       </c>
       <c r="B7" t="n">
-        <v>91316</v>
+        <v>91318</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         <v>129173765</v>
       </c>
       <c r="B9" t="n">
-        <v>91316</v>
+        <v>91318</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         <v>129173789</v>
       </c>
       <c r="B10" t="n">
-        <v>92861</v>
+        <v>92863</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>129173797</v>
       </c>
       <c r="B11" t="n">
-        <v>92861</v>
+        <v>92863</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>129173783</v>
       </c>
       <c r="B12" t="n">
-        <v>92827</v>
+        <v>92829</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
         <v>129173766</v>
       </c>
       <c r="B13" t="n">
-        <v>91316</v>
+        <v>91318</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>129173767</v>
       </c>
       <c r="B14" t="n">
-        <v>91316</v>
+        <v>91318</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>129173794</v>
       </c>
       <c r="B15" t="n">
-        <v>92861</v>
+        <v>92863</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>129173800</v>
       </c>
       <c r="B17" t="n">
-        <v>92861</v>
+        <v>92863</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>129173801</v>
       </c>
       <c r="B18" t="n">
-        <v>92861</v>
+        <v>92863</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2659,7 +2659,7 @@
         <v>129173771</v>
       </c>
       <c r="B19" t="n">
-        <v>91316</v>
+        <v>91318</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>129173803</v>
       </c>
       <c r="B20" t="n">
-        <v>92861</v>
+        <v>92863</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>129173768</v>
       </c>
       <c r="B21" t="n">
-        <v>91316</v>
+        <v>91318</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
         <v>129173770</v>
       </c>
       <c r="B22" t="n">
-        <v>91316</v>
+        <v>91318</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 221-2025 artfynd.xlsx
+++ b/artfynd/A 221-2025 artfynd.xlsx
@@ -1161,7 +1161,7 @@
         <v>129173786</v>
       </c>
       <c r="B6" t="n">
-        <v>92863</v>
+        <v>92867</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>129173764</v>
       </c>
       <c r="B7" t="n">
-        <v>91318</v>
+        <v>91322</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         <v>129173765</v>
       </c>
       <c r="B9" t="n">
-        <v>91318</v>
+        <v>91322</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         <v>129173789</v>
       </c>
       <c r="B10" t="n">
-        <v>92863</v>
+        <v>92867</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>129173797</v>
       </c>
       <c r="B11" t="n">
-        <v>92863</v>
+        <v>92867</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>129173783</v>
       </c>
       <c r="B12" t="n">
-        <v>92829</v>
+        <v>92833</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
         <v>129173766</v>
       </c>
       <c r="B13" t="n">
-        <v>91318</v>
+        <v>91322</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>129173767</v>
       </c>
       <c r="B14" t="n">
-        <v>91318</v>
+        <v>91322</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>129173794</v>
       </c>
       <c r="B15" t="n">
-        <v>92863</v>
+        <v>92867</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2424,10 +2424,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129173800</v>
+        <v>129173801</v>
       </c>
       <c r="B17" t="n">
-        <v>92863</v>
+        <v>92867</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2454,14 +2454,10 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
@@ -2470,10 +2466,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>651637</v>
+        <v>651639</v>
       </c>
       <c r="R17" t="n">
-        <v>6673909</v>
+        <v>6673915</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2505,7 +2501,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2515,7 +2511,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2542,10 +2538,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129173801</v>
+        <v>129173800</v>
       </c>
       <c r="B18" t="n">
-        <v>92863</v>
+        <v>92867</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2572,10 +2568,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
@@ -2584,10 +2584,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>651639</v>
+        <v>651637</v>
       </c>
       <c r="R18" t="n">
-        <v>6673915</v>
+        <v>6673909</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2619,7 +2619,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2629,7 +2629,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2659,7 +2659,7 @@
         <v>129173771</v>
       </c>
       <c r="B19" t="n">
-        <v>91318</v>
+        <v>91322</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>129173803</v>
       </c>
       <c r="B20" t="n">
-        <v>92863</v>
+        <v>92867</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>129173768</v>
       </c>
       <c r="B21" t="n">
-        <v>91318</v>
+        <v>91322</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
         <v>129173770</v>
       </c>
       <c r="B22" t="n">
-        <v>91318</v>
+        <v>91322</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 221-2025 artfynd.xlsx
+++ b/artfynd/A 221-2025 artfynd.xlsx
@@ -1161,7 +1161,7 @@
         <v>129173786</v>
       </c>
       <c r="B6" t="n">
-        <v>92867</v>
+        <v>92868</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>129173764</v>
       </c>
       <c r="B7" t="n">
-        <v>91322</v>
+        <v>91323</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         <v>129173765</v>
       </c>
       <c r="B9" t="n">
-        <v>91322</v>
+        <v>91323</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         <v>129173789</v>
       </c>
       <c r="B10" t="n">
-        <v>92867</v>
+        <v>92868</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>129173797</v>
       </c>
       <c r="B11" t="n">
-        <v>92867</v>
+        <v>92868</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>129173783</v>
       </c>
       <c r="B12" t="n">
-        <v>92833</v>
+        <v>92834</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
         <v>129173766</v>
       </c>
       <c r="B13" t="n">
-        <v>91322</v>
+        <v>91323</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>129173767</v>
       </c>
       <c r="B14" t="n">
-        <v>91322</v>
+        <v>91323</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>129173794</v>
       </c>
       <c r="B15" t="n">
-        <v>92867</v>
+        <v>92868</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>129173801</v>
       </c>
       <c r="B17" t="n">
-        <v>92867</v>
+        <v>92868</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>129173800</v>
       </c>
       <c r="B18" t="n">
-        <v>92867</v>
+        <v>92868</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2659,7 +2659,7 @@
         <v>129173771</v>
       </c>
       <c r="B19" t="n">
-        <v>91322</v>
+        <v>91323</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>129173803</v>
       </c>
       <c r="B20" t="n">
-        <v>92867</v>
+        <v>92868</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>129173768</v>
       </c>
       <c r="B21" t="n">
-        <v>91322</v>
+        <v>91323</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
         <v>129173770</v>
       </c>
       <c r="B22" t="n">
-        <v>91322</v>
+        <v>91323</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 221-2025 artfynd.xlsx
+++ b/artfynd/A 221-2025 artfynd.xlsx
@@ -2424,7 +2424,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129173801</v>
+        <v>129173800</v>
       </c>
       <c r="B17" t="n">
         <v>92868</v>
@@ -2454,10 +2454,14 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
@@ -2466,10 +2470,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>651639</v>
+        <v>651637</v>
       </c>
       <c r="R17" t="n">
-        <v>6673915</v>
+        <v>6673909</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2501,7 +2505,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2511,7 +2515,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2538,7 +2542,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129173800</v>
+        <v>129173801</v>
       </c>
       <c r="B18" t="n">
         <v>92868</v>
@@ -2568,14 +2572,10 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
@@ -2584,10 +2584,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>651637</v>
+        <v>651639</v>
       </c>
       <c r="R18" t="n">
-        <v>6673909</v>
+        <v>6673915</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2619,7 +2619,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2629,7 +2629,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 221-2025 artfynd.xlsx
+++ b/artfynd/A 221-2025 artfynd.xlsx
@@ -1161,7 +1161,7 @@
         <v>129173786</v>
       </c>
       <c r="B6" t="n">
-        <v>92868</v>
+        <v>92871</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>129173764</v>
       </c>
       <c r="B7" t="n">
-        <v>91323</v>
+        <v>91326</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         <v>129173765</v>
       </c>
       <c r="B9" t="n">
-        <v>91323</v>
+        <v>91326</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         <v>129173789</v>
       </c>
       <c r="B10" t="n">
-        <v>92868</v>
+        <v>92871</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>129173797</v>
       </c>
       <c r="B11" t="n">
-        <v>92868</v>
+        <v>92871</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>129173783</v>
       </c>
       <c r="B12" t="n">
-        <v>92834</v>
+        <v>92837</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
         <v>129173766</v>
       </c>
       <c r="B13" t="n">
-        <v>91323</v>
+        <v>91326</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>129173767</v>
       </c>
       <c r="B14" t="n">
-        <v>91323</v>
+        <v>91326</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>129173794</v>
       </c>
       <c r="B15" t="n">
-        <v>92868</v>
+        <v>92871</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>129173800</v>
       </c>
       <c r="B17" t="n">
-        <v>92868</v>
+        <v>92871</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>129173801</v>
       </c>
       <c r="B18" t="n">
-        <v>92868</v>
+        <v>92871</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2659,7 +2659,7 @@
         <v>129173771</v>
       </c>
       <c r="B19" t="n">
-        <v>91323</v>
+        <v>91326</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>129173803</v>
       </c>
       <c r="B20" t="n">
-        <v>92868</v>
+        <v>92871</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>129173768</v>
       </c>
       <c r="B21" t="n">
-        <v>91323</v>
+        <v>91326</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
         <v>129173770</v>
       </c>
       <c r="B22" t="n">
-        <v>91323</v>
+        <v>91326</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 221-2025 artfynd.xlsx
+++ b/artfynd/A 221-2025 artfynd.xlsx
@@ -2424,7 +2424,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129173800</v>
+        <v>129173801</v>
       </c>
       <c r="B17" t="n">
         <v>92871</v>
@@ -2454,14 +2454,10 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
@@ -2470,10 +2466,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>651637</v>
+        <v>651639</v>
       </c>
       <c r="R17" t="n">
-        <v>6673909</v>
+        <v>6673915</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2505,7 +2501,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2515,7 +2511,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2542,7 +2538,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129173801</v>
+        <v>129173800</v>
       </c>
       <c r="B18" t="n">
         <v>92871</v>
@@ -2572,10 +2568,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
@@ -2584,10 +2584,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>651639</v>
+        <v>651637</v>
       </c>
       <c r="R18" t="n">
-        <v>6673915</v>
+        <v>6673909</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2619,7 +2619,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2629,7 +2629,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 221-2025 artfynd.xlsx
+++ b/artfynd/A 221-2025 artfynd.xlsx
@@ -1161,7 +1161,7 @@
         <v>129173786</v>
       </c>
       <c r="B6" t="n">
-        <v>92871</v>
+        <v>92899</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>129173764</v>
       </c>
       <c r="B7" t="n">
-        <v>91326</v>
+        <v>91354</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>129173748</v>
       </c>
       <c r="B8" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         <v>129173765</v>
       </c>
       <c r="B9" t="n">
-        <v>91326</v>
+        <v>91354</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         <v>129173789</v>
       </c>
       <c r="B10" t="n">
-        <v>92871</v>
+        <v>92899</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>129173797</v>
       </c>
       <c r="B11" t="n">
-        <v>92871</v>
+        <v>92899</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>129173783</v>
       </c>
       <c r="B12" t="n">
-        <v>92837</v>
+        <v>92865</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
         <v>129173766</v>
       </c>
       <c r="B13" t="n">
-        <v>91326</v>
+        <v>91354</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>129173767</v>
       </c>
       <c r="B14" t="n">
-        <v>91326</v>
+        <v>91354</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>129173794</v>
       </c>
       <c r="B15" t="n">
-        <v>92871</v>
+        <v>92899</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2424,10 +2424,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129173801</v>
+        <v>129173800</v>
       </c>
       <c r="B17" t="n">
-        <v>92871</v>
+        <v>92899</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2454,10 +2454,14 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
@@ -2466,10 +2470,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>651639</v>
+        <v>651637</v>
       </c>
       <c r="R17" t="n">
-        <v>6673915</v>
+        <v>6673909</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2501,7 +2505,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2511,7 +2515,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2538,10 +2542,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129173800</v>
+        <v>129173801</v>
       </c>
       <c r="B18" t="n">
-        <v>92871</v>
+        <v>92899</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2568,14 +2572,10 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
@@ -2584,10 +2584,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>651637</v>
+        <v>651639</v>
       </c>
       <c r="R18" t="n">
-        <v>6673909</v>
+        <v>6673915</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2619,7 +2619,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2629,7 +2629,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2659,7 +2659,7 @@
         <v>129173771</v>
       </c>
       <c r="B19" t="n">
-        <v>91326</v>
+        <v>91354</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>129173803</v>
       </c>
       <c r="B20" t="n">
-        <v>92871</v>
+        <v>92899</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>129173768</v>
       </c>
       <c r="B21" t="n">
-        <v>91326</v>
+        <v>91354</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
         <v>129173770</v>
       </c>
       <c r="B22" t="n">
-        <v>91326</v>
+        <v>91354</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 221-2025 artfynd.xlsx
+++ b/artfynd/A 221-2025 artfynd.xlsx
@@ -1394,7 +1394,7 @@
         <v>129173748</v>
       </c>
       <c r="B8" t="n">
-        <v>58043</v>
+        <v>58045</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 221-2025 artfynd.xlsx
+++ b/artfynd/A 221-2025 artfynd.xlsx
@@ -1394,7 +1394,7 @@
         <v>129173748</v>
       </c>
       <c r="B8" t="n">
-        <v>58045</v>
+        <v>58046</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 221-2025 artfynd.xlsx
+++ b/artfynd/A 221-2025 artfynd.xlsx
@@ -1394,7 +1394,7 @@
         <v>129173748</v>
       </c>
       <c r="B8" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 221-2025 artfynd.xlsx
+++ b/artfynd/A 221-2025 artfynd.xlsx
@@ -1394,7 +1394,7 @@
         <v>129173748</v>
       </c>
       <c r="B8" t="n">
-        <v>58047</v>
+        <v>58050</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 221-2025 artfynd.xlsx
+++ b/artfynd/A 221-2025 artfynd.xlsx
@@ -1394,7 +1394,7 @@
         <v>129173748</v>
       </c>
       <c r="B8" t="n">
-        <v>58050</v>
+        <v>58051</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 221-2025 artfynd.xlsx
+++ b/artfynd/A 221-2025 artfynd.xlsx
@@ -1394,7 +1394,7 @@
         <v>129173748</v>
       </c>
       <c r="B8" t="n">
-        <v>58051</v>
+        <v>58057</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 221-2025 artfynd.xlsx
+++ b/artfynd/A 221-2025 artfynd.xlsx
@@ -1394,7 +1394,7 @@
         <v>129173748</v>
       </c>
       <c r="B8" t="n">
-        <v>58057</v>
+        <v>58058</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 221-2025 artfynd.xlsx
+++ b/artfynd/A 221-2025 artfynd.xlsx
@@ -1394,7 +1394,7 @@
         <v>129173748</v>
       </c>
       <c r="B8" t="n">
-        <v>58058</v>
+        <v>58061</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 221-2025 artfynd.xlsx
+++ b/artfynd/A 221-2025 artfynd.xlsx
@@ -1394,7 +1394,7 @@
         <v>129173748</v>
       </c>
       <c r="B8" t="n">
-        <v>58061</v>
+        <v>58063</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 221-2025 artfynd.xlsx
+++ b/artfynd/A 221-2025 artfynd.xlsx
@@ -1161,7 +1161,7 @@
         <v>129173786</v>
       </c>
       <c r="B6" t="n">
-        <v>92899</v>
+        <v>93216</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>129173797</v>
       </c>
       <c r="B11" t="n">
-        <v>92899</v>
+        <v>93216</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>129173794</v>
       </c>
       <c r="B15" t="n">
-        <v>92899</v>
+        <v>93216</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>129173801</v>
       </c>
       <c r="B18" t="n">
-        <v>92899</v>
+        <v>93216</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>129173803</v>
       </c>
       <c r="B20" t="n">
-        <v>92899</v>
+        <v>93216</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 221-2025 artfynd.xlsx
+++ b/artfynd/A 221-2025 artfynd.xlsx
@@ -1161,7 +1161,7 @@
         <v>129173786</v>
       </c>
       <c r="B6" t="n">
-        <v>93216</v>
+        <v>93222</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>129173797</v>
       </c>
       <c r="B11" t="n">
-        <v>93216</v>
+        <v>93222</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>129173794</v>
       </c>
       <c r="B15" t="n">
-        <v>93216</v>
+        <v>93222</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>129173801</v>
       </c>
       <c r="B18" t="n">
-        <v>93216</v>
+        <v>93222</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>129173803</v>
       </c>
       <c r="B20" t="n">
-        <v>93216</v>
+        <v>93222</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 221-2025 artfynd.xlsx
+++ b/artfynd/A 221-2025 artfynd.xlsx
@@ -1161,7 +1161,7 @@
         <v>129173786</v>
       </c>
       <c r="B6" t="n">
-        <v>93222</v>
+        <v>93232</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>129173797</v>
       </c>
       <c r="B11" t="n">
-        <v>93222</v>
+        <v>93232</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>129173794</v>
       </c>
       <c r="B15" t="n">
-        <v>93222</v>
+        <v>93232</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>129173801</v>
       </c>
       <c r="B18" t="n">
-        <v>93222</v>
+        <v>93232</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>129173803</v>
       </c>
       <c r="B20" t="n">
-        <v>93222</v>
+        <v>93232</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 221-2025 artfynd.xlsx
+++ b/artfynd/A 221-2025 artfynd.xlsx
@@ -1161,7 +1161,7 @@
         <v>129173786</v>
       </c>
       <c r="B6" t="n">
-        <v>93232</v>
+        <v>93233</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>129173797</v>
       </c>
       <c r="B11" t="n">
-        <v>93232</v>
+        <v>93233</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>129173794</v>
       </c>
       <c r="B15" t="n">
-        <v>93232</v>
+        <v>93233</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>129173801</v>
       </c>
       <c r="B18" t="n">
-        <v>93232</v>
+        <v>93233</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>129173803</v>
       </c>
       <c r="B20" t="n">
-        <v>93232</v>
+        <v>93233</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 221-2025 artfynd.xlsx
+++ b/artfynd/A 221-2025 artfynd.xlsx
@@ -1161,7 +1161,7 @@
         <v>129173786</v>
       </c>
       <c r="B6" t="n">
-        <v>93233</v>
+        <v>93234</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>129173797</v>
       </c>
       <c r="B11" t="n">
-        <v>93233</v>
+        <v>93234</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>129173794</v>
       </c>
       <c r="B15" t="n">
-        <v>93233</v>
+        <v>93234</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>129173801</v>
       </c>
       <c r="B18" t="n">
-        <v>93233</v>
+        <v>93234</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>129173803</v>
       </c>
       <c r="B20" t="n">
-        <v>93233</v>
+        <v>93234</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 221-2025 artfynd.xlsx
+++ b/artfynd/A 221-2025 artfynd.xlsx
@@ -1161,7 +1161,7 @@
         <v>129173786</v>
       </c>
       <c r="B6" t="n">
-        <v>93234</v>
+        <v>93236</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>129173797</v>
       </c>
       <c r="B11" t="n">
-        <v>93234</v>
+        <v>93236</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>129173794</v>
       </c>
       <c r="B15" t="n">
-        <v>93234</v>
+        <v>93236</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>129173801</v>
       </c>
       <c r="B18" t="n">
-        <v>93234</v>
+        <v>93236</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>129173803</v>
       </c>
       <c r="B20" t="n">
-        <v>93234</v>
+        <v>93236</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 221-2025 artfynd.xlsx
+++ b/artfynd/A 221-2025 artfynd.xlsx
@@ -1161,7 +1161,7 @@
         <v>129173786</v>
       </c>
       <c r="B6" t="n">
-        <v>93236</v>
+        <v>93237</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>129173797</v>
       </c>
       <c r="B11" t="n">
-        <v>93236</v>
+        <v>93237</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>129173794</v>
       </c>
       <c r="B15" t="n">
-        <v>93236</v>
+        <v>93237</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>129173801</v>
       </c>
       <c r="B18" t="n">
-        <v>93236</v>
+        <v>93237</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>129173803</v>
       </c>
       <c r="B20" t="n">
-        <v>93236</v>
+        <v>93237</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 221-2025 artfynd.xlsx
+++ b/artfynd/A 221-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>122330411</v>
       </c>
       <c r="B2" t="n">
-        <v>94861</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,15 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122330549</v>
+        <v>122330431</v>
       </c>
       <c r="B3" t="n">
-        <v>100510</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,21 +801,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>210</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -839,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>651558</v>
+        <v>651557</v>
       </c>
       <c r="R3" t="n">
-        <v>6673856</v>
+        <v>6673863</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -874,7 +864,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -884,7 +874,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,43 +901,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122330431</v>
+        <v>129173783</v>
       </c>
       <c r="B4" t="n">
-        <v>94861</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93199</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>210</v>
+        <v>788</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -955,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>651557</v>
+        <v>651581</v>
       </c>
       <c r="R4" t="n">
-        <v>6673863</v>
+        <v>6673839</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -985,22 +969,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Jättestort mycel!</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,37 +1016,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122330382</v>
+        <v>129173774</v>
       </c>
       <c r="B5" t="n">
-        <v>79701</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1070,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>651650</v>
+        <v>651538</v>
       </c>
       <c r="R5" t="n">
-        <v>6673900</v>
+        <v>6673932</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1100,22 +1084,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1124,24 +1108,8 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1158,10 +1126,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129173786</v>
+        <v>122330389</v>
       </c>
       <c r="B6" t="n">
-        <v>93242</v>
+        <v>91680</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1169,33 +1137,25 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5964</v>
+        <v>3215</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
@@ -1204,10 +1164,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>651568</v>
+        <v>651607</v>
       </c>
       <c r="R6" t="n">
-        <v>6673841</v>
+        <v>6673967</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1234,27 +1194,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-01-26</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-01-26</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:16</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Räknade en och en.</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1284,7 +1239,7 @@
         <v>129173764</v>
       </c>
       <c r="B7" t="n">
-        <v>91354</v>
+        <v>91680</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1391,46 +1346,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129173748</v>
+        <v>129173765</v>
       </c>
       <c r="B8" t="n">
-        <v>58063</v>
+        <v>91680</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>3215</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1438,13 +1384,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>651578</v>
+        <v>651554</v>
       </c>
       <c r="R8" t="n">
-        <v>6673850</v>
+        <v>6673844</v>
       </c>
       <c r="S8" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1473,7 +1419,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1483,7 +1429,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1510,10 +1456,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129173765</v>
+        <v>129173766</v>
       </c>
       <c r="B9" t="n">
-        <v>91354</v>
+        <v>91680</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1548,10 +1494,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>651554</v>
+        <v>651587</v>
       </c>
       <c r="R9" t="n">
-        <v>6673844</v>
+        <v>6673835</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1583,7 +1529,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1593,7 +1539,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1620,10 +1566,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129173789</v>
+        <v>129173767</v>
       </c>
       <c r="B10" t="n">
-        <v>92899</v>
+        <v>91680</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,33 +1577,25 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5964</v>
+        <v>3215</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
@@ -1666,10 +1604,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>651578</v>
+        <v>651595</v>
       </c>
       <c r="R10" t="n">
-        <v>6673861</v>
+        <v>6673879</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1701,7 +1639,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1711,7 +1649,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1738,10 +1676,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129173797</v>
+        <v>129173768</v>
       </c>
       <c r="B11" t="n">
-        <v>93242</v>
+        <v>91680</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1749,33 +1687,25 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5964</v>
+        <v>3215</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
@@ -1784,10 +1714,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>651609</v>
+        <v>651594</v>
       </c>
       <c r="R11" t="n">
-        <v>6673882</v>
+        <v>6673918</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1819,7 +1749,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1829,7 +1759,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1856,32 +1786,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129173783</v>
+        <v>129173770</v>
       </c>
       <c r="B12" t="n">
-        <v>92865</v>
+        <v>91680</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>788</v>
+        <v>3215</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1894,10 +1824,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>651581</v>
+        <v>651640</v>
       </c>
       <c r="R12" t="n">
-        <v>6673839</v>
+        <v>6673916</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1929,7 +1859,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1939,12 +1869,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:26</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Jättestort mycel!</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1971,10 +1896,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129173766</v>
+        <v>129173771</v>
       </c>
       <c r="B13" t="n">
-        <v>91354</v>
+        <v>91680</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2009,10 +1934,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>651587</v>
+        <v>651627</v>
       </c>
       <c r="R13" t="n">
-        <v>6673835</v>
+        <v>6673941</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2044,7 +1969,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2054,7 +1979,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2081,36 +2006,44 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129173767</v>
+        <v>129173786</v>
       </c>
       <c r="B14" t="n">
-        <v>91354</v>
+        <v>93307</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3215</v>
+        <v>5964</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
@@ -2119,10 +2052,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>651595</v>
+        <v>651568</v>
       </c>
       <c r="R14" t="n">
-        <v>6673879</v>
+        <v>6673841</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2154,7 +2087,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2164,7 +2097,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Räknade en och en.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2191,14 +2129,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129173794</v>
+        <v>129173789</v>
       </c>
       <c r="B15" t="n">
-        <v>93242</v>
+        <v>93233</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2221,7 +2159,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2237,10 +2175,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>651576</v>
+        <v>651578</v>
       </c>
       <c r="R15" t="n">
-        <v>6673868</v>
+        <v>6673861</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2272,7 +2210,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2282,7 +2220,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2309,41 +2247,44 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122330389</v>
+        <v>129173794</v>
       </c>
       <c r="B16" t="n">
-        <v>90609</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93307</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3215</v>
+        <v>5964</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
@@ -2352,10 +2293,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>651607</v>
+        <v>651576</v>
       </c>
       <c r="R16" t="n">
-        <v>6673967</v>
+        <v>6673868</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2382,22 +2323,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2424,14 +2365,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129173800</v>
+        <v>129173797</v>
       </c>
       <c r="B17" t="n">
-        <v>92899</v>
+        <v>93307</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2454,7 +2395,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2470,10 +2411,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>651637</v>
+        <v>651609</v>
       </c>
       <c r="R17" t="n">
-        <v>6673909</v>
+        <v>6673882</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2505,7 +2446,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2515,7 +2456,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2542,14 +2483,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129173801</v>
+        <v>129173800</v>
       </c>
       <c r="B18" t="n">
-        <v>93242</v>
+        <v>93233</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2572,10 +2513,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
@@ -2584,10 +2529,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>651639</v>
+        <v>651637</v>
       </c>
       <c r="R18" t="n">
-        <v>6673915</v>
+        <v>6673909</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2619,7 +2564,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2629,7 +2574,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2656,35 +2601,39 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129173771</v>
+        <v>129173801</v>
       </c>
       <c r="B19" t="n">
-        <v>91354</v>
+        <v>93307</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3215</v>
+        <v>5964</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
@@ -2694,10 +2643,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>651627</v>
+        <v>651639</v>
       </c>
       <c r="R19" t="n">
-        <v>6673941</v>
+        <v>6673915</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2729,7 +2678,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2739,7 +2688,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2769,11 +2718,11 @@
         <v>129173803</v>
       </c>
       <c r="B20" t="n">
-        <v>93242</v>
+        <v>93307</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2884,35 +2833,39 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129173768</v>
+        <v>129173817</v>
       </c>
       <c r="B21" t="n">
-        <v>91354</v>
+        <v>93235</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3215</v>
+        <v>5966</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
@@ -2922,10 +2875,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>651594</v>
+        <v>651525</v>
       </c>
       <c r="R21" t="n">
-        <v>6673918</v>
+        <v>6673864</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -2957,7 +2910,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2967,7 +2920,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2994,36 +2947,44 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129173770</v>
+        <v>129173819</v>
       </c>
       <c r="B22" t="n">
-        <v>91354</v>
+        <v>93235</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3215</v>
+        <v>5966</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
@@ -3032,10 +2993,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>651640</v>
+        <v>651518</v>
       </c>
       <c r="R22" t="n">
-        <v>6673916</v>
+        <v>6673884</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -3067,7 +3028,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3077,7 +3038,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3101,6 +3062,592 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>122330370</v>
+      </c>
+      <c r="B23" t="n">
+        <v>58592</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>102125</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tallbit</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Pinicola enucleator</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Ackareåsen, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>651667</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6673913</v>
+      </c>
+      <c r="S23" t="n">
+        <v>30</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>122330367</v>
+      </c>
+      <c r="B24" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Ackareåsen, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>651662</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6673914</v>
+      </c>
+      <c r="S24" t="n">
+        <v>4</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129173748</v>
+      </c>
+      <c r="B25" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Ackareåsen, Upl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>651578</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6673850</v>
+      </c>
+      <c r="S25" t="n">
+        <v>40</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>122330549</v>
+      </c>
+      <c r="B26" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Ackareåsen, Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>651558</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6673856</v>
+      </c>
+      <c r="S26" t="n">
+        <v>4</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>122330382</v>
+      </c>
+      <c r="B27" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Ackareåsen, Upl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>651650</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6673900</v>
+      </c>
+      <c r="S27" t="n">
+        <v>4</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 221-2025 artfynd.xlsx
+++ b/artfynd/A 221-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122330411</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -898,6 +908,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122330431</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1013,6 +1028,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129173783</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1123,6 +1143,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129173774</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1233,6 +1258,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122330389</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1343,6 +1373,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129173764</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1453,6 +1488,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129173765</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1563,6 +1603,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129173766</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1673,6 +1718,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129173767</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1783,6 +1833,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129173768</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1893,6 +1948,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129173770</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2003,6 +2063,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129173771</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2126,6 +2191,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129173786</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2244,6 +2314,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129173789</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2362,6 +2437,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129173794</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2480,6 +2560,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129173797</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2598,6 +2683,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129173800</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2712,6 +2802,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129173801</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2830,6 +2925,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129173803</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2944,6 +3044,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129173817</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3062,6 +3167,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129173819</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3181,6 +3291,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122330370</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3292,6 +3407,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122330367</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3411,6 +3531,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129173748</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3522,6 +3647,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122330549</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3648,8 +3778,41 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122330382</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>